--- a/tools/village-plan.xlsx
+++ b/tools/village-plan.xlsx
@@ -11,20 +11,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teams" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Packages" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workforce" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BedDemand" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accommodation" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Utilities" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transport" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VillageStaff" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuildProgramme" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capex" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opex" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CostSummary" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobilisation" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Packaging" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workforce" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BedDemand" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accommodation" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Utilities" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transport" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VillageStaff" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuildProgramme" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capex" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opex" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CostSummary" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobilisation" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -226,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -374,6 +375,18 @@
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="8" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -739,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C36"/>
+  <dimension ref="B2:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1056,12 +1069,2487 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Packages  → Packaging</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>five contracts against one prime, priced — including the break-even margin at which consolidation stops paying</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:AP30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="7.2" customWidth="1" min="3" max="3"/>
+    <col width="7.2" customWidth="1" min="4" max="4"/>
+    <col width="7.2" customWidth="1" min="5" max="5"/>
+    <col width="7.2" customWidth="1" min="6" max="6"/>
+    <col width="7.2" customWidth="1" min="7" max="7"/>
+    <col width="7.2" customWidth="1" min="8" max="8"/>
+    <col width="7.2" customWidth="1" min="9" max="9"/>
+    <col width="7.2" customWidth="1" min="10" max="10"/>
+    <col width="7.2" customWidth="1" min="11" max="11"/>
+    <col width="7.2" customWidth="1" min="12" max="12"/>
+    <col width="7.2" customWidth="1" min="13" max="13"/>
+    <col width="7.2" customWidth="1" min="14" max="14"/>
+    <col width="7.2" customWidth="1" min="15" max="15"/>
+    <col width="7.2" customWidth="1" min="16" max="16"/>
+    <col width="7.2" customWidth="1" min="17" max="17"/>
+    <col width="7.2" customWidth="1" min="18" max="18"/>
+    <col width="7.2" customWidth="1" min="19" max="19"/>
+    <col width="7.2" customWidth="1" min="20" max="20"/>
+    <col width="7.2" customWidth="1" min="21" max="21"/>
+    <col width="7.2" customWidth="1" min="22" max="22"/>
+    <col width="7.2" customWidth="1" min="23" max="23"/>
+    <col width="7.2" customWidth="1" min="24" max="24"/>
+    <col width="7.2" customWidth="1" min="25" max="25"/>
+    <col width="7.2" customWidth="1" min="26" max="26"/>
+    <col width="7.2" customWidth="1" min="27" max="27"/>
+    <col width="7.2" customWidth="1" min="28" max="28"/>
+    <col width="7.2" customWidth="1" min="29" max="29"/>
+    <col width="7.2" customWidth="1" min="30" max="30"/>
+    <col width="7.2" customWidth="1" min="31" max="31"/>
+    <col width="7.2" customWidth="1" min="32" max="32"/>
+    <col width="7.2" customWidth="1" min="33" max="33"/>
+    <col width="7.2" customWidth="1" min="34" max="34"/>
+    <col width="7.2" customWidth="1" min="35" max="35"/>
+    <col width="7.2" customWidth="1" min="36" max="36"/>
+    <col width="7.2" customWidth="1" min="37" max="37"/>
+    <col width="7.2" customWidth="1" min="38" max="38"/>
+    <col width="7.2" customWidth="1" min="39" max="39"/>
+    <col width="7.2" customWidth="1" min="40" max="40"/>
+    <col width="62" customWidth="1" min="42" max="42"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>UTILITIES, ENERGY AND WASTE — MONTH BY MONTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Driven by occupancy from BedDemand. Design against the peak; budget against the curve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C5" s="36">
+        <f>Workforce!C5</f>
+        <v/>
+      </c>
+      <c r="D5" s="36">
+        <f>Workforce!D5</f>
+        <v/>
+      </c>
+      <c r="E5" s="36">
+        <f>Workforce!E5</f>
+        <v/>
+      </c>
+      <c r="F5" s="36">
+        <f>Workforce!F5</f>
+        <v/>
+      </c>
+      <c r="G5" s="36">
+        <f>Workforce!G5</f>
+        <v/>
+      </c>
+      <c r="H5" s="36">
+        <f>Workforce!H5</f>
+        <v/>
+      </c>
+      <c r="I5" s="36">
+        <f>Workforce!I5</f>
+        <v/>
+      </c>
+      <c r="J5" s="36">
+        <f>Workforce!J5</f>
+        <v/>
+      </c>
+      <c r="K5" s="36">
+        <f>Workforce!K5</f>
+        <v/>
+      </c>
+      <c r="L5" s="36">
+        <f>Workforce!L5</f>
+        <v/>
+      </c>
+      <c r="M5" s="36">
+        <f>Workforce!M5</f>
+        <v/>
+      </c>
+      <c r="N5" s="36">
+        <f>Workforce!N5</f>
+        <v/>
+      </c>
+      <c r="O5" s="36">
+        <f>Workforce!O5</f>
+        <v/>
+      </c>
+      <c r="P5" s="36">
+        <f>Workforce!P5</f>
+        <v/>
+      </c>
+      <c r="Q5" s="36">
+        <f>Workforce!Q5</f>
+        <v/>
+      </c>
+      <c r="R5" s="36">
+        <f>Workforce!R5</f>
+        <v/>
+      </c>
+      <c r="S5" s="36">
+        <f>Workforce!S5</f>
+        <v/>
+      </c>
+      <c r="T5" s="36">
+        <f>Workforce!T5</f>
+        <v/>
+      </c>
+      <c r="U5" s="36">
+        <f>Workforce!U5</f>
+        <v/>
+      </c>
+      <c r="V5" s="36">
+        <f>Workforce!V5</f>
+        <v/>
+      </c>
+      <c r="W5" s="36">
+        <f>Workforce!W5</f>
+        <v/>
+      </c>
+      <c r="X5" s="36">
+        <f>Workforce!X5</f>
+        <v/>
+      </c>
+      <c r="Y5" s="36">
+        <f>Workforce!Y5</f>
+        <v/>
+      </c>
+      <c r="Z5" s="36">
+        <f>Workforce!Z5</f>
+        <v/>
+      </c>
+      <c r="AA5" s="36">
+        <f>Workforce!AA5</f>
+        <v/>
+      </c>
+      <c r="AB5" s="36">
+        <f>Workforce!AB5</f>
+        <v/>
+      </c>
+      <c r="AC5" s="36">
+        <f>Workforce!AC5</f>
+        <v/>
+      </c>
+      <c r="AD5" s="36">
+        <f>Workforce!AD5</f>
+        <v/>
+      </c>
+      <c r="AE5" s="36">
+        <f>Workforce!AE5</f>
+        <v/>
+      </c>
+      <c r="AF5" s="36">
+        <f>Workforce!AF5</f>
+        <v/>
+      </c>
+      <c r="AG5" s="36">
+        <f>Workforce!AG5</f>
+        <v/>
+      </c>
+      <c r="AH5" s="36">
+        <f>Workforce!AH5</f>
+        <v/>
+      </c>
+      <c r="AI5" s="36">
+        <f>Workforce!AI5</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="36">
+        <f>Workforce!AJ5</f>
+        <v/>
+      </c>
+      <c r="AK5" s="36">
+        <f>Workforce!AK5</f>
+        <v/>
+      </c>
+      <c r="AL5" s="36">
+        <f>Workforce!AL5</f>
+        <v/>
+      </c>
+      <c r="AM5" s="36">
+        <f>Workforce!AM5</f>
+        <v/>
+      </c>
+      <c r="AN5" s="36">
+        <f>Workforce!AN5</f>
+        <v/>
+      </c>
+      <c r="AP5" s="6" t="inlineStr">
+        <is>
+          <t>Basis, and what to verify</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Month number</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="L6" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="M6" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="O6" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="P6" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q6" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="R6" s="32" t="n">
+        <v>16</v>
+      </c>
+      <c r="S6" s="32" t="n">
+        <v>17</v>
+      </c>
+      <c r="T6" s="32" t="n">
+        <v>18</v>
+      </c>
+      <c r="U6" s="32" t="n">
+        <v>19</v>
+      </c>
+      <c r="V6" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="W6" s="32" t="n">
+        <v>21</v>
+      </c>
+      <c r="X6" s="32" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y6" s="32" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z6" s="32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA6" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB6" s="32" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC6" s="32" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD6" s="32" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE6" s="32" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF6" s="32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG6" s="32" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH6" s="32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI6" s="32" t="n">
+        <v>33</v>
+      </c>
+      <c r="AJ6" s="32" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK6" s="32" t="n">
+        <v>35</v>
+      </c>
+      <c r="AL6" s="32" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM6" s="32" t="n">
+        <v>37</v>
+      </c>
+      <c r="AN6" s="32" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Residents in village</t>
+        </is>
+      </c>
+      <c r="C7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!C10</t>
+        </is>
+      </c>
+      <c r="D7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!D10</t>
+        </is>
+      </c>
+      <c r="E7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!E10</t>
+        </is>
+      </c>
+      <c r="F7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!F10</t>
+        </is>
+      </c>
+      <c r="G7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!G10</t>
+        </is>
+      </c>
+      <c r="H7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!H10</t>
+        </is>
+      </c>
+      <c r="I7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!I10</t>
+        </is>
+      </c>
+      <c r="J7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!J10</t>
+        </is>
+      </c>
+      <c r="K7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!K10</t>
+        </is>
+      </c>
+      <c r="L7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!L10</t>
+        </is>
+      </c>
+      <c r="M7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!M10</t>
+        </is>
+      </c>
+      <c r="N7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!N10</t>
+        </is>
+      </c>
+      <c r="O7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!O10</t>
+        </is>
+      </c>
+      <c r="P7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!P10</t>
+        </is>
+      </c>
+      <c r="Q7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!Q10</t>
+        </is>
+      </c>
+      <c r="R7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!R10</t>
+        </is>
+      </c>
+      <c r="S7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!S10</t>
+        </is>
+      </c>
+      <c r="T7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!T10</t>
+        </is>
+      </c>
+      <c r="U7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!U10</t>
+        </is>
+      </c>
+      <c r="V7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!V10</t>
+        </is>
+      </c>
+      <c r="W7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!W10</t>
+        </is>
+      </c>
+      <c r="X7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!X10</t>
+        </is>
+      </c>
+      <c r="Y7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!Y10</t>
+        </is>
+      </c>
+      <c r="Z7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!Z10</t>
+        </is>
+      </c>
+      <c r="AA7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!AA10</t>
+        </is>
+      </c>
+      <c r="AB7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!AB10</t>
+        </is>
+      </c>
+      <c r="AC7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!AC10</t>
+        </is>
+      </c>
+      <c r="AD7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!AD10</t>
+        </is>
+      </c>
+      <c r="AE7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!AE10</t>
+        </is>
+      </c>
+      <c r="AF7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!AF10</t>
+        </is>
+      </c>
+      <c r="AG7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!AG10</t>
+        </is>
+      </c>
+      <c r="AH7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!AH10</t>
+        </is>
+      </c>
+      <c r="AI7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!AI10</t>
+        </is>
+      </c>
+      <c r="AJ7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!AJ10</t>
+        </is>
+      </c>
+      <c r="AK7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!AK10</t>
+        </is>
+      </c>
+      <c r="AL7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!AL10</t>
+        </is>
+      </c>
+      <c r="AM7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!AM10</t>
+        </is>
+      </c>
+      <c r="AN7" s="58" t="inlineStr">
+        <is>
+          <t>BedDemand!AN10</t>
+        </is>
+      </c>
+      <c r="AP7" s="57" t="inlineStr">
+        <is>
+          <t>From BedDemand. Everything on this sheet follows it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Water demand</t>
+        </is>
+      </c>
+      <c r="C9" s="59">
+        <f>ROUND(BedDemand!C10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="D9" s="59">
+        <f>ROUND(BedDemand!D10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="E9" s="59">
+        <f>ROUND(BedDemand!E10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="F9" s="59">
+        <f>ROUND(BedDemand!F10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="G9" s="59">
+        <f>ROUND(BedDemand!G10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="H9" s="59">
+        <f>ROUND(BedDemand!H10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="I9" s="59">
+        <f>ROUND(BedDemand!I10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="J9" s="59">
+        <f>ROUND(BedDemand!J10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="K9" s="59">
+        <f>ROUND(BedDemand!K10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="L9" s="59">
+        <f>ROUND(BedDemand!L10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="M9" s="59">
+        <f>ROUND(BedDemand!M10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="N9" s="59">
+        <f>ROUND(BedDemand!N10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="O9" s="59">
+        <f>ROUND(BedDemand!O10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="P9" s="59">
+        <f>ROUND(BedDemand!P10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="Q9" s="59">
+        <f>ROUND(BedDemand!Q10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="R9" s="59">
+        <f>ROUND(BedDemand!R10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="S9" s="59">
+        <f>ROUND(BedDemand!S10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="T9" s="59">
+        <f>ROUND(BedDemand!T10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="U9" s="59">
+        <f>ROUND(BedDemand!U10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="V9" s="59">
+        <f>ROUND(BedDemand!V10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="W9" s="59">
+        <f>ROUND(BedDemand!W10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="X9" s="59">
+        <f>ROUND(BedDemand!X10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="Y9" s="59">
+        <f>ROUND(BedDemand!Y10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="Z9" s="59">
+        <f>ROUND(BedDemand!Z10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="AA9" s="59">
+        <f>ROUND(BedDemand!AA10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="AB9" s="59">
+        <f>ROUND(BedDemand!AB10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="AC9" s="59">
+        <f>ROUND(BedDemand!AC10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="AD9" s="59">
+        <f>ROUND(BedDemand!AD10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="AE9" s="59">
+        <f>ROUND(BedDemand!AE10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="AF9" s="59">
+        <f>ROUND(BedDemand!AF10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="AG9" s="59">
+        <f>ROUND(BedDemand!AG10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="AH9" s="59">
+        <f>ROUND(BedDemand!AH10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="AI9" s="59">
+        <f>ROUND(BedDemand!AI10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="59">
+        <f>ROUND(BedDemand!AJ10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="AK9" s="59">
+        <f>ROUND(BedDemand!AK10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="AL9" s="59">
+        <f>ROUND(BedDemand!AL10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="AM9" s="59">
+        <f>ROUND(BedDemand!AM10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="AN9" s="59">
+        <f>ROUND(BedDemand!AN10*Assumptions!$C$51/1000,1)</f>
+        <v/>
+      </c>
+      <c r="AP9" s="57" t="inlineStr">
+        <is>
+          <t>m³/day. Residential occupancy — showers, laundry, catering, WCs. Far above a site-welfare figure. Verify with the water undertaker before relying on a connection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of which hot water</t>
+        </is>
+      </c>
+      <c r="C10" s="59">
+        <f>ROUND(C9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="D10" s="59">
+        <f>ROUND(D9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="E10" s="59">
+        <f>ROUND(E9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="F10" s="59">
+        <f>ROUND(F9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="G10" s="59">
+        <f>ROUND(G9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="H10" s="59">
+        <f>ROUND(H9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="I10" s="59">
+        <f>ROUND(I9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="J10" s="59">
+        <f>ROUND(J9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="K10" s="59">
+        <f>ROUND(K9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="L10" s="59">
+        <f>ROUND(L9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="M10" s="59">
+        <f>ROUND(M9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="N10" s="59">
+        <f>ROUND(N9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="O10" s="59">
+        <f>ROUND(O9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="P10" s="59">
+        <f>ROUND(P9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="Q10" s="59">
+        <f>ROUND(Q9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="R10" s="59">
+        <f>ROUND(R9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="S10" s="59">
+        <f>ROUND(S9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="T10" s="59">
+        <f>ROUND(T9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="U10" s="59">
+        <f>ROUND(U9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="V10" s="59">
+        <f>ROUND(V9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="W10" s="59">
+        <f>ROUND(W9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="X10" s="59">
+        <f>ROUND(X9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="Y10" s="59">
+        <f>ROUND(Y9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="Z10" s="59">
+        <f>ROUND(Z9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="AA10" s="59">
+        <f>ROUND(AA9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="AB10" s="59">
+        <f>ROUND(AB9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="AC10" s="59">
+        <f>ROUND(AC9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="AD10" s="59">
+        <f>ROUND(AD9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="AE10" s="59">
+        <f>ROUND(AE9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="AF10" s="59">
+        <f>ROUND(AF9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="AG10" s="59">
+        <f>ROUND(AG9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="AH10" s="59">
+        <f>ROUND(AH9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="AI10" s="59">
+        <f>ROUND(AI9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="59">
+        <f>ROUND(AJ9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="AK10" s="59">
+        <f>ROUND(AK9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="AL10" s="59">
+        <f>ROUND(AL9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="AM10" s="59">
+        <f>ROUND(AM9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="AN10" s="59">
+        <f>ROUND(AN9*Assumptions!$C$52,1)</f>
+        <v/>
+      </c>
+      <c r="AP10" s="57" t="inlineStr">
+        <is>
+          <t>m³/day. Sizes calorifiers and the heating load that serves them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Foul return</t>
+        </is>
+      </c>
+      <c r="C11" s="59">
+        <f>ROUND(C9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="D11" s="59">
+        <f>ROUND(D9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="E11" s="59">
+        <f>ROUND(E9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="F11" s="59">
+        <f>ROUND(F9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="G11" s="59">
+        <f>ROUND(G9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="H11" s="59">
+        <f>ROUND(H9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="I11" s="59">
+        <f>ROUND(I9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="J11" s="59">
+        <f>ROUND(J9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="K11" s="59">
+        <f>ROUND(K9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="L11" s="59">
+        <f>ROUND(L9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="M11" s="59">
+        <f>ROUND(M9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="N11" s="59">
+        <f>ROUND(N9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="O11" s="59">
+        <f>ROUND(O9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="P11" s="59">
+        <f>ROUND(P9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="Q11" s="59">
+        <f>ROUND(Q9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="R11" s="59">
+        <f>ROUND(R9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="S11" s="59">
+        <f>ROUND(S9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="T11" s="59">
+        <f>ROUND(T9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="U11" s="59">
+        <f>ROUND(U9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="V11" s="59">
+        <f>ROUND(V9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="W11" s="59">
+        <f>ROUND(W9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="X11" s="59">
+        <f>ROUND(X9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="Y11" s="59">
+        <f>ROUND(Y9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="Z11" s="59">
+        <f>ROUND(Z9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="AA11" s="59">
+        <f>ROUND(AA9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="AB11" s="59">
+        <f>ROUND(AB9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="AC11" s="59">
+        <f>ROUND(AC9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="AD11" s="59">
+        <f>ROUND(AD9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="AE11" s="59">
+        <f>ROUND(AE9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="AF11" s="59">
+        <f>ROUND(AF9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="AG11" s="59">
+        <f>ROUND(AG9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="AH11" s="59">
+        <f>ROUND(AH9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="AI11" s="59">
+        <f>ROUND(AI9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="59">
+        <f>ROUND(AJ9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="AK11" s="59">
+        <f>ROUND(AK9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="AL11" s="59">
+        <f>ROUND(AL9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="AM11" s="59">
+        <f>ROUND(AM9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="AN11" s="59">
+        <f>ROUND(AN9*Assumptions!$C$53,1)</f>
+        <v/>
+      </c>
+      <c r="AP11" s="57" t="inlineStr">
+        <is>
+          <t>m³/day. Treatment plant capacity, or tanker frequency if there is no connection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Tanker movements if no foul connection</t>
+        </is>
+      </c>
+      <c r="C12" s="59">
+        <f>ROUNDUP(C11/30,0)</f>
+        <v/>
+      </c>
+      <c r="D12" s="59">
+        <f>ROUNDUP(D11/30,0)</f>
+        <v/>
+      </c>
+      <c r="E12" s="59">
+        <f>ROUNDUP(E11/30,0)</f>
+        <v/>
+      </c>
+      <c r="F12" s="59">
+        <f>ROUNDUP(F11/30,0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="59">
+        <f>ROUNDUP(G11/30,0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="59">
+        <f>ROUNDUP(H11/30,0)</f>
+        <v/>
+      </c>
+      <c r="I12" s="59">
+        <f>ROUNDUP(I11/30,0)</f>
+        <v/>
+      </c>
+      <c r="J12" s="59">
+        <f>ROUNDUP(J11/30,0)</f>
+        <v/>
+      </c>
+      <c r="K12" s="59">
+        <f>ROUNDUP(K11/30,0)</f>
+        <v/>
+      </c>
+      <c r="L12" s="59">
+        <f>ROUNDUP(L11/30,0)</f>
+        <v/>
+      </c>
+      <c r="M12" s="59">
+        <f>ROUNDUP(M11/30,0)</f>
+        <v/>
+      </c>
+      <c r="N12" s="59">
+        <f>ROUNDUP(N11/30,0)</f>
+        <v/>
+      </c>
+      <c r="O12" s="59">
+        <f>ROUNDUP(O11/30,0)</f>
+        <v/>
+      </c>
+      <c r="P12" s="59">
+        <f>ROUNDUP(P11/30,0)</f>
+        <v/>
+      </c>
+      <c r="Q12" s="59">
+        <f>ROUNDUP(Q11/30,0)</f>
+        <v/>
+      </c>
+      <c r="R12" s="59">
+        <f>ROUNDUP(R11/30,0)</f>
+        <v/>
+      </c>
+      <c r="S12" s="59">
+        <f>ROUNDUP(S11/30,0)</f>
+        <v/>
+      </c>
+      <c r="T12" s="59">
+        <f>ROUNDUP(T11/30,0)</f>
+        <v/>
+      </c>
+      <c r="U12" s="59">
+        <f>ROUNDUP(U11/30,0)</f>
+        <v/>
+      </c>
+      <c r="V12" s="59">
+        <f>ROUNDUP(V11/30,0)</f>
+        <v/>
+      </c>
+      <c r="W12" s="59">
+        <f>ROUNDUP(W11/30,0)</f>
+        <v/>
+      </c>
+      <c r="X12" s="59">
+        <f>ROUNDUP(X11/30,0)</f>
+        <v/>
+      </c>
+      <c r="Y12" s="59">
+        <f>ROUNDUP(Y11/30,0)</f>
+        <v/>
+      </c>
+      <c r="Z12" s="59">
+        <f>ROUNDUP(Z11/30,0)</f>
+        <v/>
+      </c>
+      <c r="AA12" s="59">
+        <f>ROUNDUP(AA11/30,0)</f>
+        <v/>
+      </c>
+      <c r="AB12" s="59">
+        <f>ROUNDUP(AB11/30,0)</f>
+        <v/>
+      </c>
+      <c r="AC12" s="59">
+        <f>ROUNDUP(AC11/30,0)</f>
+        <v/>
+      </c>
+      <c r="AD12" s="59">
+        <f>ROUNDUP(AD11/30,0)</f>
+        <v/>
+      </c>
+      <c r="AE12" s="59">
+        <f>ROUNDUP(AE11/30,0)</f>
+        <v/>
+      </c>
+      <c r="AF12" s="59">
+        <f>ROUNDUP(AF11/30,0)</f>
+        <v/>
+      </c>
+      <c r="AG12" s="59">
+        <f>ROUNDUP(AG11/30,0)</f>
+        <v/>
+      </c>
+      <c r="AH12" s="59">
+        <f>ROUNDUP(AH11/30,0)</f>
+        <v/>
+      </c>
+      <c r="AI12" s="59">
+        <f>ROUNDUP(AI11/30,0)</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="59">
+        <f>ROUNDUP(AJ11/30,0)</f>
+        <v/>
+      </c>
+      <c r="AK12" s="59">
+        <f>ROUNDUP(AK11/30,0)</f>
+        <v/>
+      </c>
+      <c r="AL12" s="59">
+        <f>ROUNDUP(AL11/30,0)</f>
+        <v/>
+      </c>
+      <c r="AM12" s="59">
+        <f>ROUNDUP(AM11/30,0)</f>
+        <v/>
+      </c>
+      <c r="AN12" s="59">
+        <f>ROUNDUP(AN11/30,0)</f>
+        <v/>
+      </c>
+      <c r="AP12" s="57" t="inlineStr">
+        <is>
+          <t>loads/day at 30 m³ a tanker. If this number is above one or two, a connection or a package plant stops being optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Electrical connected load</t>
+        </is>
+      </c>
+      <c r="C14" s="60">
+        <f>ROUND(BedDemand!C10*Assumptions!$C$54+IF(BedDemand!C10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="D14" s="60">
+        <f>ROUND(BedDemand!D10*Assumptions!$C$54+IF(BedDemand!D10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="E14" s="60">
+        <f>ROUND(BedDemand!E10*Assumptions!$C$54+IF(BedDemand!E10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="F14" s="60">
+        <f>ROUND(BedDemand!F10*Assumptions!$C$54+IF(BedDemand!F10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="60">
+        <f>ROUND(BedDemand!G10*Assumptions!$C$54+IF(BedDemand!G10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="60">
+        <f>ROUND(BedDemand!H10*Assumptions!$C$54+IF(BedDemand!H10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="I14" s="60">
+        <f>ROUND(BedDemand!I10*Assumptions!$C$54+IF(BedDemand!I10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="J14" s="60">
+        <f>ROUND(BedDemand!J10*Assumptions!$C$54+IF(BedDemand!J10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="K14" s="60">
+        <f>ROUND(BedDemand!K10*Assumptions!$C$54+IF(BedDemand!K10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="L14" s="60">
+        <f>ROUND(BedDemand!L10*Assumptions!$C$54+IF(BedDemand!L10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="M14" s="60">
+        <f>ROUND(BedDemand!M10*Assumptions!$C$54+IF(BedDemand!M10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="N14" s="60">
+        <f>ROUND(BedDemand!N10*Assumptions!$C$54+IF(BedDemand!N10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="O14" s="60">
+        <f>ROUND(BedDemand!O10*Assumptions!$C$54+IF(BedDemand!O10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="P14" s="60">
+        <f>ROUND(BedDemand!P10*Assumptions!$C$54+IF(BedDemand!P10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="60">
+        <f>ROUND(BedDemand!Q10*Assumptions!$C$54+IF(BedDemand!Q10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="R14" s="60">
+        <f>ROUND(BedDemand!R10*Assumptions!$C$54+IF(BedDemand!R10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="S14" s="60">
+        <f>ROUND(BedDemand!S10*Assumptions!$C$54+IF(BedDemand!S10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="T14" s="60">
+        <f>ROUND(BedDemand!T10*Assumptions!$C$54+IF(BedDemand!T10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="U14" s="60">
+        <f>ROUND(BedDemand!U10*Assumptions!$C$54+IF(BedDemand!U10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="V14" s="60">
+        <f>ROUND(BedDemand!V10*Assumptions!$C$54+IF(BedDemand!V10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="W14" s="60">
+        <f>ROUND(BedDemand!W10*Assumptions!$C$54+IF(BedDemand!W10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="X14" s="60">
+        <f>ROUND(BedDemand!X10*Assumptions!$C$54+IF(BedDemand!X10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="Y14" s="60">
+        <f>ROUND(BedDemand!Y10*Assumptions!$C$54+IF(BedDemand!Y10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="Z14" s="60">
+        <f>ROUND(BedDemand!Z10*Assumptions!$C$54+IF(BedDemand!Z10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="AA14" s="60">
+        <f>ROUND(BedDemand!AA10*Assumptions!$C$54+IF(BedDemand!AA10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="AB14" s="60">
+        <f>ROUND(BedDemand!AB10*Assumptions!$C$54+IF(BedDemand!AB10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="AC14" s="60">
+        <f>ROUND(BedDemand!AC10*Assumptions!$C$54+IF(BedDemand!AC10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="AD14" s="60">
+        <f>ROUND(BedDemand!AD10*Assumptions!$C$54+IF(BedDemand!AD10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="AE14" s="60">
+        <f>ROUND(BedDemand!AE10*Assumptions!$C$54+IF(BedDemand!AE10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="AF14" s="60">
+        <f>ROUND(BedDemand!AF10*Assumptions!$C$54+IF(BedDemand!AF10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="AG14" s="60">
+        <f>ROUND(BedDemand!AG10*Assumptions!$C$54+IF(BedDemand!AG10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="AH14" s="60">
+        <f>ROUND(BedDemand!AH10*Assumptions!$C$54+IF(BedDemand!AH10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="AI14" s="60">
+        <f>ROUND(BedDemand!AI10*Assumptions!$C$54+IF(BedDemand!AI10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="AJ14" s="60">
+        <f>ROUND(BedDemand!AJ10*Assumptions!$C$54+IF(BedDemand!AJ10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="AK14" s="60">
+        <f>ROUND(BedDemand!AK10*Assumptions!$C$54+IF(BedDemand!AK10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="AL14" s="60">
+        <f>ROUND(BedDemand!AL10*Assumptions!$C$54+IF(BedDemand!AL10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="AM14" s="60">
+        <f>ROUND(BedDemand!AM10*Assumptions!$C$54+IF(BedDemand!AM10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="AN14" s="60">
+        <f>ROUND(BedDemand!AN10*Assumptions!$C$54+IF(BedDemand!AN10&gt;0,Assumptions!$C$56,0),0)</f>
+        <v/>
+      </c>
+      <c r="AP14" s="57" t="inlineStr">
+        <is>
+          <t>kW. Accommodation plus catering. Excludes electric space heating, which is on the line below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Heating load</t>
+        </is>
+      </c>
+      <c r="C15" s="60">
+        <f>ROUND(BedDemand!C10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="60">
+        <f>ROUND(BedDemand!D10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="E15" s="60">
+        <f>ROUND(BedDemand!E10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="F15" s="60">
+        <f>ROUND(BedDemand!F10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="60">
+        <f>ROUND(BedDemand!G10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="60">
+        <f>ROUND(BedDemand!H10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="I15" s="60">
+        <f>ROUND(BedDemand!I10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="J15" s="60">
+        <f>ROUND(BedDemand!J10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="K15" s="60">
+        <f>ROUND(BedDemand!K10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="L15" s="60">
+        <f>ROUND(BedDemand!L10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="M15" s="60">
+        <f>ROUND(BedDemand!M10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="N15" s="60">
+        <f>ROUND(BedDemand!N10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="O15" s="60">
+        <f>ROUND(BedDemand!O10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="P15" s="60">
+        <f>ROUND(BedDemand!P10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="Q15" s="60">
+        <f>ROUND(BedDemand!Q10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="R15" s="60">
+        <f>ROUND(BedDemand!R10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="S15" s="60">
+        <f>ROUND(BedDemand!S10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="T15" s="60">
+        <f>ROUND(BedDemand!T10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="U15" s="60">
+        <f>ROUND(BedDemand!U10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="V15" s="60">
+        <f>ROUND(BedDemand!V10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="W15" s="60">
+        <f>ROUND(BedDemand!W10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="X15" s="60">
+        <f>ROUND(BedDemand!X10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="Y15" s="60">
+        <f>ROUND(BedDemand!Y10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="Z15" s="60">
+        <f>ROUND(BedDemand!Z10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="AA15" s="60">
+        <f>ROUND(BedDemand!AA10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="AB15" s="60">
+        <f>ROUND(BedDemand!AB10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="AC15" s="60">
+        <f>ROUND(BedDemand!AC10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="AD15" s="60">
+        <f>ROUND(BedDemand!AD10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="AE15" s="60">
+        <f>ROUND(BedDemand!AE10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="AF15" s="60">
+        <f>ROUND(BedDemand!AF10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="AG15" s="60">
+        <f>ROUND(BedDemand!AG10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="AH15" s="60">
+        <f>ROUND(BedDemand!AH10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="AI15" s="60">
+        <f>ROUND(BedDemand!AI10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="AJ15" s="60">
+        <f>ROUND(BedDemand!AJ10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="AK15" s="60">
+        <f>ROUND(BedDemand!AK10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="AL15" s="60">
+        <f>ROUND(BedDemand!AL10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="AM15" s="60">
+        <f>ROUND(BedDemand!AM10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="AN15" s="60">
+        <f>ROUND(BedDemand!AN10*Assumptions!$C$57,0)</f>
+        <v/>
+      </c>
+      <c r="AP15" s="57" t="inlineStr">
+        <is>
+          <t>kW at design outside temperature. Verify against the module supplier's U-values and the fuel you actually use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Diversified demand</t>
+        </is>
+      </c>
+      <c r="C16" s="60">
+        <f>ROUND(C14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="60">
+        <f>ROUND(D14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="E16" s="60">
+        <f>ROUND(E14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="F16" s="60">
+        <f>ROUND(F14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="60">
+        <f>ROUND(G14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="60">
+        <f>ROUND(H14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="I16" s="60">
+        <f>ROUND(I14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="J16" s="60">
+        <f>ROUND(J14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="K16" s="60">
+        <f>ROUND(K14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="L16" s="60">
+        <f>ROUND(L14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="M16" s="60">
+        <f>ROUND(M14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="N16" s="60">
+        <f>ROUND(N14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="O16" s="60">
+        <f>ROUND(O14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="P16" s="60">
+        <f>ROUND(P14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="Q16" s="60">
+        <f>ROUND(Q14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="R16" s="60">
+        <f>ROUND(R14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="S16" s="60">
+        <f>ROUND(S14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="T16" s="60">
+        <f>ROUND(T14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="U16" s="60">
+        <f>ROUND(U14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="V16" s="60">
+        <f>ROUND(V14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="W16" s="60">
+        <f>ROUND(W14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="X16" s="60">
+        <f>ROUND(X14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="Y16" s="60">
+        <f>ROUND(Y14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="Z16" s="60">
+        <f>ROUND(Z14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="AA16" s="60">
+        <f>ROUND(AA14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="AB16" s="60">
+        <f>ROUND(AB14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="AC16" s="60">
+        <f>ROUND(AC14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="AD16" s="60">
+        <f>ROUND(AD14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="AE16" s="60">
+        <f>ROUND(AE14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="AF16" s="60">
+        <f>ROUND(AF14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="AG16" s="60">
+        <f>ROUND(AG14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="AH16" s="60">
+        <f>ROUND(AH14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="AI16" s="60">
+        <f>ROUND(AI14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="AJ16" s="60">
+        <f>ROUND(AJ14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="AK16" s="60">
+        <f>ROUND(AK14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="AL16" s="60">
+        <f>ROUND(AL14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="AM16" s="60">
+        <f>ROUND(AM14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="AN16" s="60">
+        <f>ROUND(AN14*Assumptions!$C$55,0)</f>
+        <v/>
+      </c>
+      <c r="AP16" s="57" t="inlineStr">
+        <is>
+          <t>kW. Not every load runs at once. The diversity factor is on Assumptions and needs an engineer's eye.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Diversified demand</t>
+        </is>
+      </c>
+      <c r="C17" s="60">
+        <f>ROUND(C16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="60">
+        <f>ROUND(D16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="E17" s="60">
+        <f>ROUND(E16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="F17" s="60">
+        <f>ROUND(F16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="60">
+        <f>ROUND(G16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="H17" s="60">
+        <f>ROUND(H16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="I17" s="60">
+        <f>ROUND(I16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="J17" s="60">
+        <f>ROUND(J16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="K17" s="60">
+        <f>ROUND(K16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="L17" s="60">
+        <f>ROUND(L16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="M17" s="60">
+        <f>ROUND(M16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="N17" s="60">
+        <f>ROUND(N16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="O17" s="60">
+        <f>ROUND(O16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="P17" s="60">
+        <f>ROUND(P16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="Q17" s="60">
+        <f>ROUND(Q16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="R17" s="60">
+        <f>ROUND(R16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="S17" s="60">
+        <f>ROUND(S16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="T17" s="60">
+        <f>ROUND(T16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="U17" s="60">
+        <f>ROUND(U16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="V17" s="60">
+        <f>ROUND(V16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="W17" s="60">
+        <f>ROUND(W16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="X17" s="60">
+        <f>ROUND(X16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="Y17" s="60">
+        <f>ROUND(Y16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="Z17" s="60">
+        <f>ROUND(Z16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="AA17" s="60">
+        <f>ROUND(AA16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="AB17" s="60">
+        <f>ROUND(AB16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="AC17" s="60">
+        <f>ROUND(AC16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="AD17" s="60">
+        <f>ROUND(AD16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="AE17" s="60">
+        <f>ROUND(AE16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="AF17" s="60">
+        <f>ROUND(AF16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="AG17" s="60">
+        <f>ROUND(AG16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="AH17" s="60">
+        <f>ROUND(AH16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="AI17" s="60">
+        <f>ROUND(AI16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="AJ17" s="60">
+        <f>ROUND(AJ16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="AK17" s="60">
+        <f>ROUND(AK16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="AL17" s="60">
+        <f>ROUND(AL16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="AM17" s="60">
+        <f>ROUND(AM16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="AN17" s="60">
+        <f>ROUND(AN16/Assumptions!$C$58,0)</f>
+        <v/>
+      </c>
+      <c r="AP17" s="57" t="inlineStr">
+        <is>
+          <t>kVA — the unit a DNO connection or a generator is actually sized in. Getting kW and kVA confused undersizes a village by a fifth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Waste arisings</t>
+        </is>
+      </c>
+      <c r="C19" s="59">
+        <f>ROUND(BedDemand!C10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="D19" s="59">
+        <f>ROUND(BedDemand!D10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="E19" s="59">
+        <f>ROUND(BedDemand!E10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="F19" s="59">
+        <f>ROUND(BedDemand!F10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="G19" s="59">
+        <f>ROUND(BedDemand!G10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="H19" s="59">
+        <f>ROUND(BedDemand!H10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="I19" s="59">
+        <f>ROUND(BedDemand!I10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="J19" s="59">
+        <f>ROUND(BedDemand!J10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="K19" s="59">
+        <f>ROUND(BedDemand!K10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="L19" s="59">
+        <f>ROUND(BedDemand!L10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="M19" s="59">
+        <f>ROUND(BedDemand!M10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="N19" s="59">
+        <f>ROUND(BedDemand!N10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="O19" s="59">
+        <f>ROUND(BedDemand!O10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="P19" s="59">
+        <f>ROUND(BedDemand!P10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="Q19" s="59">
+        <f>ROUND(BedDemand!Q10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="R19" s="59">
+        <f>ROUND(BedDemand!R10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="S19" s="59">
+        <f>ROUND(BedDemand!S10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="T19" s="59">
+        <f>ROUND(BedDemand!T10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="U19" s="59">
+        <f>ROUND(BedDemand!U10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="V19" s="59">
+        <f>ROUND(BedDemand!V10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="W19" s="59">
+        <f>ROUND(BedDemand!W10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="X19" s="59">
+        <f>ROUND(BedDemand!X10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="Y19" s="59">
+        <f>ROUND(BedDemand!Y10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="Z19" s="59">
+        <f>ROUND(BedDemand!Z10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="AA19" s="59">
+        <f>ROUND(BedDemand!AA10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="AB19" s="59">
+        <f>ROUND(BedDemand!AB10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="AC19" s="59">
+        <f>ROUND(BedDemand!AC10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="AD19" s="59">
+        <f>ROUND(BedDemand!AD10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="AE19" s="59">
+        <f>ROUND(BedDemand!AE10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="AF19" s="59">
+        <f>ROUND(BedDemand!AF10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="AG19" s="59">
+        <f>ROUND(BedDemand!AG10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="AH19" s="59">
+        <f>ROUND(BedDemand!AH10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="AI19" s="59">
+        <f>ROUND(BedDemand!AI10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="59">
+        <f>ROUND(BedDemand!AJ10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="AK19" s="59">
+        <f>ROUND(BedDemand!AK10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="AL19" s="59">
+        <f>ROUND(BedDemand!AL10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="AM19" s="59">
+        <f>ROUND(BedDemand!AM10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="AN19" s="59">
+        <f>ROUND(BedDemand!AN10*Assumptions!$C$59/1000*30.4,1)</f>
+        <v/>
+      </c>
+      <c r="AP19" s="57" t="inlineStr">
+        <is>
+          <t>tonnes/month. Residential plus catering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  recycled or diverted</t>
+        </is>
+      </c>
+      <c r="C20" s="59">
+        <f>ROUND(C19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="D20" s="59">
+        <f>ROUND(D19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="E20" s="59">
+        <f>ROUND(E19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="F20" s="59">
+        <f>ROUND(F19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="G20" s="59">
+        <f>ROUND(G19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="H20" s="59">
+        <f>ROUND(H19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="I20" s="59">
+        <f>ROUND(I19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="J20" s="59">
+        <f>ROUND(J19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="K20" s="59">
+        <f>ROUND(K19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="L20" s="59">
+        <f>ROUND(L19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="M20" s="59">
+        <f>ROUND(M19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="N20" s="59">
+        <f>ROUND(N19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="O20" s="59">
+        <f>ROUND(O19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="P20" s="59">
+        <f>ROUND(P19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="59">
+        <f>ROUND(Q19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="R20" s="59">
+        <f>ROUND(R19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="S20" s="59">
+        <f>ROUND(S19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="T20" s="59">
+        <f>ROUND(T19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="U20" s="59">
+        <f>ROUND(U19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="V20" s="59">
+        <f>ROUND(V19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="W20" s="59">
+        <f>ROUND(W19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="X20" s="59">
+        <f>ROUND(X19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="Y20" s="59">
+        <f>ROUND(Y19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="Z20" s="59">
+        <f>ROUND(Z19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="AA20" s="59">
+        <f>ROUND(AA19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="AB20" s="59">
+        <f>ROUND(AB19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="AC20" s="59">
+        <f>ROUND(AC19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="AD20" s="59">
+        <f>ROUND(AD19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="AE20" s="59">
+        <f>ROUND(AE19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="AF20" s="59">
+        <f>ROUND(AF19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="AG20" s="59">
+        <f>ROUND(AG19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="AH20" s="59">
+        <f>ROUND(AH19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="AI20" s="59">
+        <f>ROUND(AI19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="AJ20" s="59">
+        <f>ROUND(AJ19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="AK20" s="59">
+        <f>ROUND(AK19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="AL20" s="59">
+        <f>ROUND(AL19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="AM20" s="59">
+        <f>ROUND(AM19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="AN20" s="59">
+        <f>ROUND(AN19*Assumptions!$C$60,1)</f>
+        <v/>
+      </c>
+      <c r="AP20" s="57" t="inlineStr">
+        <is>
+          <t>tonnes/month against the target on Assumptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>General waste collections</t>
+        </is>
+      </c>
+      <c r="C21" s="37">
+        <f>ROUNDUP(C19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="D21" s="37">
+        <f>ROUNDUP(D19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="E21" s="37">
+        <f>ROUNDUP(E19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="F21" s="37">
+        <f>ROUNDUP(F19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="G21" s="37">
+        <f>ROUNDUP(G19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="H21" s="37">
+        <f>ROUNDUP(H19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="I21" s="37">
+        <f>ROUNDUP(I19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="J21" s="37">
+        <f>ROUNDUP(J19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="37">
+        <f>ROUNDUP(K19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="L21" s="37">
+        <f>ROUNDUP(L19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="M21" s="37">
+        <f>ROUNDUP(M19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="N21" s="37">
+        <f>ROUNDUP(N19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="O21" s="37">
+        <f>ROUNDUP(O19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="P21" s="37">
+        <f>ROUNDUP(P19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="37">
+        <f>ROUNDUP(Q19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="R21" s="37">
+        <f>ROUNDUP(R19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="S21" s="37">
+        <f>ROUNDUP(S19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="T21" s="37">
+        <f>ROUNDUP(T19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="U21" s="37">
+        <f>ROUNDUP(U19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="V21" s="37">
+        <f>ROUNDUP(V19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="W21" s="37">
+        <f>ROUNDUP(W19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="X21" s="37">
+        <f>ROUNDUP(X19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="Y21" s="37">
+        <f>ROUNDUP(Y19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="Z21" s="37">
+        <f>ROUNDUP(Z19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="AA21" s="37">
+        <f>ROUNDUP(AA19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="AB21" s="37">
+        <f>ROUNDUP(AB19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="AC21" s="37">
+        <f>ROUNDUP(AC19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="AD21" s="37">
+        <f>ROUNDUP(AD19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="AE21" s="37">
+        <f>ROUNDUP(AE19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="AF21" s="37">
+        <f>ROUNDUP(AF19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="AG21" s="37">
+        <f>ROUNDUP(AG19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="AH21" s="37">
+        <f>ROUNDUP(AH19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="AI21" s="37">
+        <f>ROUNDUP(AI19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="AJ21" s="37">
+        <f>ROUNDUP(AJ19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="AK21" s="37">
+        <f>ROUNDUP(AK19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="AL21" s="37">
+        <f>ROUNDUP(AL19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="AM21" s="37">
+        <f>ROUNDUP(AM19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="AN21" s="37">
+        <f>ROUNDUP(AN19*1000/1100/12,0)</f>
+        <v/>
+      </c>
+      <c r="AP21" s="57" t="inlineStr">
+        <is>
+          <t>collections/month at 1100 l bins, twelve per collection. Indicative — set against the contractor's actual round.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="39" t="inlineStr">
+        <is>
+          <t>PEAK — WHAT YOU DESIGN AND PROCURE AGAINST</t>
+        </is>
+      </c>
+      <c r="C23" s="40" t="n"/>
+      <c r="D23" s="40" t="n"/>
+      <c r="E23" s="40" t="n"/>
+      <c r="F23" s="40" t="n"/>
+      <c r="G23" s="40" t="n"/>
+      <c r="H23" s="40" t="n"/>
+      <c r="I23" s="40" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Peak water demand</t>
+        </is>
+      </c>
+      <c r="C24" s="61">
+        <f>MAX(C9:AN9)</f>
+        <v/>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>m³/day — the figure that goes on the water undertaker's enquiry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Peak foul return</t>
+        </is>
+      </c>
+      <c r="C25" s="61">
+        <f>MAX(C11:AN11)</f>
+        <v/>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>m³/day — treatment plant or tanker capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Peak connected load</t>
+        </is>
+      </c>
+      <c r="C26" s="62">
+        <f>MAX(C14:AN14)</f>
+        <v/>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>kW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Peak diversified demand</t>
+        </is>
+      </c>
+      <c r="C27" s="62">
+        <f>MAX(C17:AN17)</f>
+        <v/>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>kVA — the figure that goes on the DNO application or the generator enquiry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Peak waste arisings</t>
+        </is>
+      </c>
+      <c r="C28" s="61">
+        <f>MAX(C19:AN19)</f>
+        <v/>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>tonnes/month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="63" t="inlineStr">
+        <is>
+          <t>Every figure on this sheet is a first-pass planning figure requiring validation by a competent person before it is procured against.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3146,7 +5634,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5590,7 +8078,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6710,7 +9198,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7466,7 +9954,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9327,7 +11815,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9993,7 +12481,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10574,7 +13062,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11261,7 +13749,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15510,6 +17998,555 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:F34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="2" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>FIVE CONTRACTS, OR ONE — MODELLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Splitting the village into five packages buys competition on each. Letting it as one buys an owner for the whole. This sheet prices the difference instead of arguing about it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="91" t="inlineStr"/>
+      <c r="B5" s="91" t="inlineStr"/>
+      <c r="C5" s="92" t="inlineStr">
+        <is>
+          <t>FIVE PACKAGES</t>
+        </is>
+      </c>
+      <c r="D5" s="92" t="inlineStr">
+        <is>
+          <t>ONE PRIME</t>
+        </is>
+      </c>
+      <c r="E5" s="91" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F5" s="91" t="inlineStr">
+        <is>
+          <t>Basis — and what to test</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>WHAT YOU ARE BUYING</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Contracts the client holds</t>
+        </is>
+      </c>
+      <c r="C7" s="93" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>no.</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>Change the left-hand figure if you split differently. Everything below follows it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Interfaces the client owns</t>
+        </is>
+      </c>
+      <c r="C8" s="50">
+        <f>C7*(C7-1)/2</f>
+        <v/>
+      </c>
+      <c r="D8" s="50">
+        <f>D7*(D7-1)/2</f>
+        <v/>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>no.</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>n(n−1)/2. Five contracts is ten interfaces; one is none — they move inside the prime, they do not disappear. The Packages sheet lists fifteen because several involve three parties.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Direct package cost — capex</t>
+        </is>
+      </c>
+      <c r="C9" s="71">
+        <f>Capex!$D$26+Capex!$D$27+Capex!$D$28+Capex!$D$29+Capex!$D$30</f>
+        <v/>
+      </c>
+      <c r="D9" s="71">
+        <f>C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>£</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>The same physical village either way. Consolidation does not change what gets built.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Direct package cost — opex over the programme</t>
+        </is>
+      </c>
+      <c r="C10" s="71">
+        <f>Opex!$AP$14</f>
+        <v/>
+      </c>
+      <c r="D10" s="71">
+        <f>C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>£</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>Same.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>WHAT THE CLIENT SPENDS TO MANAGE IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Client-side management FTE</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>Package managers, commercial and coordination on the client's own payroll. One prime is not zero — somebody still holds the prime to account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Loaded cost per FTE per month</t>
+        </is>
+      </c>
+      <c r="C13" s="94" t="n">
+        <v>9500</v>
+      </c>
+      <c r="D13" s="94">
+        <f>C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>£</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>INDICATIVE. Replace with your own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Months of management</t>
+        </is>
+      </c>
+      <c r="C14" s="93" t="n">
+        <v>44</v>
+      </c>
+      <c r="D14" s="93">
+        <f>C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>Programme plus procurement and closeout at both ends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Client management cost</t>
+        </is>
+      </c>
+      <c r="C15" s="71">
+        <f>C12*C13*C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="71">
+        <f>D12*D13*D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>£</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>The line that is always paid and rarely counted, because it sits in overhead rather than in the package.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>WHAT THE INTERFACES COST</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Average cost when an interface fails</t>
+        </is>
+      </c>
+      <c r="C17" s="94" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D17" s="94">
+        <f>C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>£</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>INDICATIVE. Craneage standing, a re-order, a fortnight of programme. Set it from your own experience — this is the number you actually know better than the model does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Probability an unowned interface bites</t>
+        </is>
+      </c>
+      <c r="C18" s="95" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D18" s="95" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>Five packages: roughly a third of unowned interfaces cost money. Under a prime the interface still exists but somebody owns it, so the residual is what leaks past them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Expected interface cost</t>
+        </is>
+      </c>
+      <c r="C19" s="71">
+        <f>C8*C17*C18</f>
+        <v/>
+      </c>
+      <c r="D19" s="71">
+        <f>C8*C17*D18</f>
+        <v/>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>£</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>Note the prime column still uses the same interface count. Consolidation does not remove interfaces; it gives them an owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>WHAT THE PRIME CHARGES FOR TAKING IT ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Prime margin on the packages</t>
+        </is>
+      </c>
+      <c r="C21" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="96" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>The premium for one throat to choke. Nobody carries interface risk for nothing. 8.5% is INDICATIVE — this is the number to negotiate and the number to test below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Prime margin cost</t>
+        </is>
+      </c>
+      <c r="C22" s="71">
+        <f>(C9+C10)*C21</f>
+        <v/>
+      </c>
+      <c r="D22" s="71">
+        <f>(D9+D10)*D21</f>
+        <v/>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>£</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr"/>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Procurement and tendering cost</t>
+        </is>
+      </c>
+      <c r="C23" s="94" t="n">
+        <v>95000</v>
+      </c>
+      <c r="D23" s="94" t="n">
+        <v>42000</v>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>£</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>Five ITTs, five evaluations, five negotiations, five contracts — against one. INDICATIVE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>THE ANSWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>TOTAL COST TO THE CLIENT</t>
+        </is>
+      </c>
+      <c r="C25" s="97">
+        <f>C9+C10+C15+C19+C22+C23</f>
+        <v/>
+      </c>
+      <c r="D25" s="97">
+        <f>D9+D10+D15+D19+D22+D23</f>
+        <v/>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>£</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="C26" s="97" t="inlineStr"/>
+      <c r="D26" s="97">
+        <f>C25-D25</f>
+        <v/>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>£</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>Positive means one prime is cheaper on these assumptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Break-even prime margin</t>
+        </is>
+      </c>
+      <c r="C27" s="98" t="inlineStr"/>
+      <c r="D27" s="98">
+        <f>IFERROR((C25-D9-D10-D15-D19-D23)/(D9+D10),0)</f>
+        <v/>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>Above this margin, five packages win. Below it, the prime does. This is the single number to take into the negotiation — and the one worth knowing before the first conversation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   WHAT THE MODEL DOES NOT PRICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>·  Programme. A prime can sequence across packages; five contractors each protect their own float and none of them owns the critical path between them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>·  Single point of accountability when it goes wrong at 02:00 on a Sunday. This has a value and it is not in any of the cells above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>·  Competition. Five packages are competed five ways; a prime is competed once and then you are married to it for 38 months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>·  Supply chain access. A prime with standing relationships can buy better than a client buying five packages cold — sometimes enough to fund its own margin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>·  The consolidation route itself. Appointing five and then novating them under one is a third option, and it is the one that keeps the competition and buys the ownership. It is also the hardest to contract, which is why it is worth being the person who has done it.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A29:F29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19626,7 +22663,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24160,7 +27197,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24581,7 +27618,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25118,2467 +28155,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:AP30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="7.2" customWidth="1" min="3" max="3"/>
-    <col width="7.2" customWidth="1" min="4" max="4"/>
-    <col width="7.2" customWidth="1" min="5" max="5"/>
-    <col width="7.2" customWidth="1" min="6" max="6"/>
-    <col width="7.2" customWidth="1" min="7" max="7"/>
-    <col width="7.2" customWidth="1" min="8" max="8"/>
-    <col width="7.2" customWidth="1" min="9" max="9"/>
-    <col width="7.2" customWidth="1" min="10" max="10"/>
-    <col width="7.2" customWidth="1" min="11" max="11"/>
-    <col width="7.2" customWidth="1" min="12" max="12"/>
-    <col width="7.2" customWidth="1" min="13" max="13"/>
-    <col width="7.2" customWidth="1" min="14" max="14"/>
-    <col width="7.2" customWidth="1" min="15" max="15"/>
-    <col width="7.2" customWidth="1" min="16" max="16"/>
-    <col width="7.2" customWidth="1" min="17" max="17"/>
-    <col width="7.2" customWidth="1" min="18" max="18"/>
-    <col width="7.2" customWidth="1" min="19" max="19"/>
-    <col width="7.2" customWidth="1" min="20" max="20"/>
-    <col width="7.2" customWidth="1" min="21" max="21"/>
-    <col width="7.2" customWidth="1" min="22" max="22"/>
-    <col width="7.2" customWidth="1" min="23" max="23"/>
-    <col width="7.2" customWidth="1" min="24" max="24"/>
-    <col width="7.2" customWidth="1" min="25" max="25"/>
-    <col width="7.2" customWidth="1" min="26" max="26"/>
-    <col width="7.2" customWidth="1" min="27" max="27"/>
-    <col width="7.2" customWidth="1" min="28" max="28"/>
-    <col width="7.2" customWidth="1" min="29" max="29"/>
-    <col width="7.2" customWidth="1" min="30" max="30"/>
-    <col width="7.2" customWidth="1" min="31" max="31"/>
-    <col width="7.2" customWidth="1" min="32" max="32"/>
-    <col width="7.2" customWidth="1" min="33" max="33"/>
-    <col width="7.2" customWidth="1" min="34" max="34"/>
-    <col width="7.2" customWidth="1" min="35" max="35"/>
-    <col width="7.2" customWidth="1" min="36" max="36"/>
-    <col width="7.2" customWidth="1" min="37" max="37"/>
-    <col width="7.2" customWidth="1" min="38" max="38"/>
-    <col width="7.2" customWidth="1" min="39" max="39"/>
-    <col width="7.2" customWidth="1" min="40" max="40"/>
-    <col width="62" customWidth="1" min="42" max="42"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>UTILITIES, ENERGY AND WASTE — MONTH BY MONTH</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Driven by occupancy from BedDemand. Design against the peak; budget against the curve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="C5" s="36">
-        <f>Workforce!C5</f>
-        <v/>
-      </c>
-      <c r="D5" s="36">
-        <f>Workforce!D5</f>
-        <v/>
-      </c>
-      <c r="E5" s="36">
-        <f>Workforce!E5</f>
-        <v/>
-      </c>
-      <c r="F5" s="36">
-        <f>Workforce!F5</f>
-        <v/>
-      </c>
-      <c r="G5" s="36">
-        <f>Workforce!G5</f>
-        <v/>
-      </c>
-      <c r="H5" s="36">
-        <f>Workforce!H5</f>
-        <v/>
-      </c>
-      <c r="I5" s="36">
-        <f>Workforce!I5</f>
-        <v/>
-      </c>
-      <c r="J5" s="36">
-        <f>Workforce!J5</f>
-        <v/>
-      </c>
-      <c r="K5" s="36">
-        <f>Workforce!K5</f>
-        <v/>
-      </c>
-      <c r="L5" s="36">
-        <f>Workforce!L5</f>
-        <v/>
-      </c>
-      <c r="M5" s="36">
-        <f>Workforce!M5</f>
-        <v/>
-      </c>
-      <c r="N5" s="36">
-        <f>Workforce!N5</f>
-        <v/>
-      </c>
-      <c r="O5" s="36">
-        <f>Workforce!O5</f>
-        <v/>
-      </c>
-      <c r="P5" s="36">
-        <f>Workforce!P5</f>
-        <v/>
-      </c>
-      <c r="Q5" s="36">
-        <f>Workforce!Q5</f>
-        <v/>
-      </c>
-      <c r="R5" s="36">
-        <f>Workforce!R5</f>
-        <v/>
-      </c>
-      <c r="S5" s="36">
-        <f>Workforce!S5</f>
-        <v/>
-      </c>
-      <c r="T5" s="36">
-        <f>Workforce!T5</f>
-        <v/>
-      </c>
-      <c r="U5" s="36">
-        <f>Workforce!U5</f>
-        <v/>
-      </c>
-      <c r="V5" s="36">
-        <f>Workforce!V5</f>
-        <v/>
-      </c>
-      <c r="W5" s="36">
-        <f>Workforce!W5</f>
-        <v/>
-      </c>
-      <c r="X5" s="36">
-        <f>Workforce!X5</f>
-        <v/>
-      </c>
-      <c r="Y5" s="36">
-        <f>Workforce!Y5</f>
-        <v/>
-      </c>
-      <c r="Z5" s="36">
-        <f>Workforce!Z5</f>
-        <v/>
-      </c>
-      <c r="AA5" s="36">
-        <f>Workforce!AA5</f>
-        <v/>
-      </c>
-      <c r="AB5" s="36">
-        <f>Workforce!AB5</f>
-        <v/>
-      </c>
-      <c r="AC5" s="36">
-        <f>Workforce!AC5</f>
-        <v/>
-      </c>
-      <c r="AD5" s="36">
-        <f>Workforce!AD5</f>
-        <v/>
-      </c>
-      <c r="AE5" s="36">
-        <f>Workforce!AE5</f>
-        <v/>
-      </c>
-      <c r="AF5" s="36">
-        <f>Workforce!AF5</f>
-        <v/>
-      </c>
-      <c r="AG5" s="36">
-        <f>Workforce!AG5</f>
-        <v/>
-      </c>
-      <c r="AH5" s="36">
-        <f>Workforce!AH5</f>
-        <v/>
-      </c>
-      <c r="AI5" s="36">
-        <f>Workforce!AI5</f>
-        <v/>
-      </c>
-      <c r="AJ5" s="36">
-        <f>Workforce!AJ5</f>
-        <v/>
-      </c>
-      <c r="AK5" s="36">
-        <f>Workforce!AK5</f>
-        <v/>
-      </c>
-      <c r="AL5" s="36">
-        <f>Workforce!AL5</f>
-        <v/>
-      </c>
-      <c r="AM5" s="36">
-        <f>Workforce!AM5</f>
-        <v/>
-      </c>
-      <c r="AN5" s="36">
-        <f>Workforce!AN5</f>
-        <v/>
-      </c>
-      <c r="AP5" s="6" t="inlineStr">
-        <is>
-          <t>Basis, and what to verify</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Month number</t>
-        </is>
-      </c>
-      <c r="C6" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="I6" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="J6" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="K6" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="L6" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="M6" s="32" t="n">
-        <v>11</v>
-      </c>
-      <c r="N6" s="32" t="n">
-        <v>12</v>
-      </c>
-      <c r="O6" s="32" t="n">
-        <v>13</v>
-      </c>
-      <c r="P6" s="32" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q6" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="R6" s="32" t="n">
-        <v>16</v>
-      </c>
-      <c r="S6" s="32" t="n">
-        <v>17</v>
-      </c>
-      <c r="T6" s="32" t="n">
-        <v>18</v>
-      </c>
-      <c r="U6" s="32" t="n">
-        <v>19</v>
-      </c>
-      <c r="V6" s="32" t="n">
-        <v>20</v>
-      </c>
-      <c r="W6" s="32" t="n">
-        <v>21</v>
-      </c>
-      <c r="X6" s="32" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y6" s="32" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z6" s="32" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA6" s="32" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB6" s="32" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC6" s="32" t="n">
-        <v>27</v>
-      </c>
-      <c r="AD6" s="32" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE6" s="32" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF6" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG6" s="32" t="n">
-        <v>31</v>
-      </c>
-      <c r="AH6" s="32" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI6" s="32" t="n">
-        <v>33</v>
-      </c>
-      <c r="AJ6" s="32" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK6" s="32" t="n">
-        <v>35</v>
-      </c>
-      <c r="AL6" s="32" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM6" s="32" t="n">
-        <v>37</v>
-      </c>
-      <c r="AN6" s="32" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Residents in village</t>
-        </is>
-      </c>
-      <c r="C7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!C10</t>
-        </is>
-      </c>
-      <c r="D7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!D10</t>
-        </is>
-      </c>
-      <c r="E7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!E10</t>
-        </is>
-      </c>
-      <c r="F7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!F10</t>
-        </is>
-      </c>
-      <c r="G7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!G10</t>
-        </is>
-      </c>
-      <c r="H7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!H10</t>
-        </is>
-      </c>
-      <c r="I7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!I10</t>
-        </is>
-      </c>
-      <c r="J7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!J10</t>
-        </is>
-      </c>
-      <c r="K7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!K10</t>
-        </is>
-      </c>
-      <c r="L7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!L10</t>
-        </is>
-      </c>
-      <c r="M7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!M10</t>
-        </is>
-      </c>
-      <c r="N7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!N10</t>
-        </is>
-      </c>
-      <c r="O7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!O10</t>
-        </is>
-      </c>
-      <c r="P7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!P10</t>
-        </is>
-      </c>
-      <c r="Q7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!Q10</t>
-        </is>
-      </c>
-      <c r="R7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!R10</t>
-        </is>
-      </c>
-      <c r="S7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!S10</t>
-        </is>
-      </c>
-      <c r="T7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!T10</t>
-        </is>
-      </c>
-      <c r="U7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!U10</t>
-        </is>
-      </c>
-      <c r="V7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!V10</t>
-        </is>
-      </c>
-      <c r="W7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!W10</t>
-        </is>
-      </c>
-      <c r="X7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!X10</t>
-        </is>
-      </c>
-      <c r="Y7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!Y10</t>
-        </is>
-      </c>
-      <c r="Z7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!Z10</t>
-        </is>
-      </c>
-      <c r="AA7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!AA10</t>
-        </is>
-      </c>
-      <c r="AB7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!AB10</t>
-        </is>
-      </c>
-      <c r="AC7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!AC10</t>
-        </is>
-      </c>
-      <c r="AD7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!AD10</t>
-        </is>
-      </c>
-      <c r="AE7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!AE10</t>
-        </is>
-      </c>
-      <c r="AF7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!AF10</t>
-        </is>
-      </c>
-      <c r="AG7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!AG10</t>
-        </is>
-      </c>
-      <c r="AH7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!AH10</t>
-        </is>
-      </c>
-      <c r="AI7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!AI10</t>
-        </is>
-      </c>
-      <c r="AJ7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!AJ10</t>
-        </is>
-      </c>
-      <c r="AK7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!AK10</t>
-        </is>
-      </c>
-      <c r="AL7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!AL10</t>
-        </is>
-      </c>
-      <c r="AM7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!AM10</t>
-        </is>
-      </c>
-      <c r="AN7" s="58" t="inlineStr">
-        <is>
-          <t>BedDemand!AN10</t>
-        </is>
-      </c>
-      <c r="AP7" s="57" t="inlineStr">
-        <is>
-          <t>From BedDemand. Everything on this sheet follows it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Water demand</t>
-        </is>
-      </c>
-      <c r="C9" s="59">
-        <f>ROUND(BedDemand!C10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="D9" s="59">
-        <f>ROUND(BedDemand!D10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="E9" s="59">
-        <f>ROUND(BedDemand!E10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="F9" s="59">
-        <f>ROUND(BedDemand!F10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="G9" s="59">
-        <f>ROUND(BedDemand!G10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="H9" s="59">
-        <f>ROUND(BedDemand!H10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="I9" s="59">
-        <f>ROUND(BedDemand!I10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="J9" s="59">
-        <f>ROUND(BedDemand!J10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="K9" s="59">
-        <f>ROUND(BedDemand!K10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="L9" s="59">
-        <f>ROUND(BedDemand!L10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="M9" s="59">
-        <f>ROUND(BedDemand!M10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="N9" s="59">
-        <f>ROUND(BedDemand!N10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="O9" s="59">
-        <f>ROUND(BedDemand!O10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="P9" s="59">
-        <f>ROUND(BedDemand!P10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="Q9" s="59">
-        <f>ROUND(BedDemand!Q10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="R9" s="59">
-        <f>ROUND(BedDemand!R10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="S9" s="59">
-        <f>ROUND(BedDemand!S10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="T9" s="59">
-        <f>ROUND(BedDemand!T10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="U9" s="59">
-        <f>ROUND(BedDemand!U10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="V9" s="59">
-        <f>ROUND(BedDemand!V10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="W9" s="59">
-        <f>ROUND(BedDemand!W10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="X9" s="59">
-        <f>ROUND(BedDemand!X10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="Y9" s="59">
-        <f>ROUND(BedDemand!Y10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="Z9" s="59">
-        <f>ROUND(BedDemand!Z10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="AA9" s="59">
-        <f>ROUND(BedDemand!AA10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="AB9" s="59">
-        <f>ROUND(BedDemand!AB10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="AC9" s="59">
-        <f>ROUND(BedDemand!AC10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="AD9" s="59">
-        <f>ROUND(BedDemand!AD10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="AE9" s="59">
-        <f>ROUND(BedDemand!AE10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="AF9" s="59">
-        <f>ROUND(BedDemand!AF10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="AG9" s="59">
-        <f>ROUND(BedDemand!AG10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="AH9" s="59">
-        <f>ROUND(BedDemand!AH10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="AI9" s="59">
-        <f>ROUND(BedDemand!AI10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="AJ9" s="59">
-        <f>ROUND(BedDemand!AJ10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="AK9" s="59">
-        <f>ROUND(BedDemand!AK10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="AL9" s="59">
-        <f>ROUND(BedDemand!AL10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="AM9" s="59">
-        <f>ROUND(BedDemand!AM10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="AN9" s="59">
-        <f>ROUND(BedDemand!AN10*Assumptions!$C$51/1000,1)</f>
-        <v/>
-      </c>
-      <c r="AP9" s="57" t="inlineStr">
-        <is>
-          <t>m³/day. Residential occupancy — showers, laundry, catering, WCs. Far above a site-welfare figure. Verify with the water undertaker before relying on a connection.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  of which hot water</t>
-        </is>
-      </c>
-      <c r="C10" s="59">
-        <f>ROUND(C9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="D10" s="59">
-        <f>ROUND(D9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="E10" s="59">
-        <f>ROUND(E9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="F10" s="59">
-        <f>ROUND(F9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="G10" s="59">
-        <f>ROUND(G9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="H10" s="59">
-        <f>ROUND(H9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="I10" s="59">
-        <f>ROUND(I9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="J10" s="59">
-        <f>ROUND(J9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="K10" s="59">
-        <f>ROUND(K9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="L10" s="59">
-        <f>ROUND(L9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="M10" s="59">
-        <f>ROUND(M9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="N10" s="59">
-        <f>ROUND(N9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="O10" s="59">
-        <f>ROUND(O9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="P10" s="59">
-        <f>ROUND(P9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="Q10" s="59">
-        <f>ROUND(Q9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="R10" s="59">
-        <f>ROUND(R9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="S10" s="59">
-        <f>ROUND(S9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="T10" s="59">
-        <f>ROUND(T9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="U10" s="59">
-        <f>ROUND(U9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="V10" s="59">
-        <f>ROUND(V9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="W10" s="59">
-        <f>ROUND(W9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="X10" s="59">
-        <f>ROUND(X9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="Y10" s="59">
-        <f>ROUND(Y9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="Z10" s="59">
-        <f>ROUND(Z9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="AA10" s="59">
-        <f>ROUND(AA9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="AB10" s="59">
-        <f>ROUND(AB9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="AC10" s="59">
-        <f>ROUND(AC9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="AD10" s="59">
-        <f>ROUND(AD9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="AE10" s="59">
-        <f>ROUND(AE9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="AF10" s="59">
-        <f>ROUND(AF9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="AG10" s="59">
-        <f>ROUND(AG9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="AH10" s="59">
-        <f>ROUND(AH9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="AI10" s="59">
-        <f>ROUND(AI9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="AJ10" s="59">
-        <f>ROUND(AJ9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="AK10" s="59">
-        <f>ROUND(AK9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="AL10" s="59">
-        <f>ROUND(AL9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="AM10" s="59">
-        <f>ROUND(AM9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="AN10" s="59">
-        <f>ROUND(AN9*Assumptions!$C$52,1)</f>
-        <v/>
-      </c>
-      <c r="AP10" s="57" t="inlineStr">
-        <is>
-          <t>m³/day. Sizes calorifiers and the heating load that serves them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Foul return</t>
-        </is>
-      </c>
-      <c r="C11" s="59">
-        <f>ROUND(C9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="D11" s="59">
-        <f>ROUND(D9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="E11" s="59">
-        <f>ROUND(E9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="F11" s="59">
-        <f>ROUND(F9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="G11" s="59">
-        <f>ROUND(G9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="H11" s="59">
-        <f>ROUND(H9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="I11" s="59">
-        <f>ROUND(I9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="J11" s="59">
-        <f>ROUND(J9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="K11" s="59">
-        <f>ROUND(K9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="L11" s="59">
-        <f>ROUND(L9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="M11" s="59">
-        <f>ROUND(M9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="N11" s="59">
-        <f>ROUND(N9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="O11" s="59">
-        <f>ROUND(O9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="P11" s="59">
-        <f>ROUND(P9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="Q11" s="59">
-        <f>ROUND(Q9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="R11" s="59">
-        <f>ROUND(R9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="S11" s="59">
-        <f>ROUND(S9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="T11" s="59">
-        <f>ROUND(T9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="U11" s="59">
-        <f>ROUND(U9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="V11" s="59">
-        <f>ROUND(V9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="W11" s="59">
-        <f>ROUND(W9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="X11" s="59">
-        <f>ROUND(X9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="Y11" s="59">
-        <f>ROUND(Y9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="Z11" s="59">
-        <f>ROUND(Z9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="AA11" s="59">
-        <f>ROUND(AA9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="AB11" s="59">
-        <f>ROUND(AB9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="AC11" s="59">
-        <f>ROUND(AC9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="AD11" s="59">
-        <f>ROUND(AD9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="AE11" s="59">
-        <f>ROUND(AE9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="AF11" s="59">
-        <f>ROUND(AF9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="AG11" s="59">
-        <f>ROUND(AG9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="AH11" s="59">
-        <f>ROUND(AH9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="AI11" s="59">
-        <f>ROUND(AI9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="AJ11" s="59">
-        <f>ROUND(AJ9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="AK11" s="59">
-        <f>ROUND(AK9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="AL11" s="59">
-        <f>ROUND(AL9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="AM11" s="59">
-        <f>ROUND(AM9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="AN11" s="59">
-        <f>ROUND(AN9*Assumptions!$C$53,1)</f>
-        <v/>
-      </c>
-      <c r="AP11" s="57" t="inlineStr">
-        <is>
-          <t>m³/day. Treatment plant capacity, or tanker frequency if there is no connection.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Tanker movements if no foul connection</t>
-        </is>
-      </c>
-      <c r="C12" s="59">
-        <f>ROUNDUP(C11/30,0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="59">
-        <f>ROUNDUP(D11/30,0)</f>
-        <v/>
-      </c>
-      <c r="E12" s="59">
-        <f>ROUNDUP(E11/30,0)</f>
-        <v/>
-      </c>
-      <c r="F12" s="59">
-        <f>ROUNDUP(F11/30,0)</f>
-        <v/>
-      </c>
-      <c r="G12" s="59">
-        <f>ROUNDUP(G11/30,0)</f>
-        <v/>
-      </c>
-      <c r="H12" s="59">
-        <f>ROUNDUP(H11/30,0)</f>
-        <v/>
-      </c>
-      <c r="I12" s="59">
-        <f>ROUNDUP(I11/30,0)</f>
-        <v/>
-      </c>
-      <c r="J12" s="59">
-        <f>ROUNDUP(J11/30,0)</f>
-        <v/>
-      </c>
-      <c r="K12" s="59">
-        <f>ROUNDUP(K11/30,0)</f>
-        <v/>
-      </c>
-      <c r="L12" s="59">
-        <f>ROUNDUP(L11/30,0)</f>
-        <v/>
-      </c>
-      <c r="M12" s="59">
-        <f>ROUNDUP(M11/30,0)</f>
-        <v/>
-      </c>
-      <c r="N12" s="59">
-        <f>ROUNDUP(N11/30,0)</f>
-        <v/>
-      </c>
-      <c r="O12" s="59">
-        <f>ROUNDUP(O11/30,0)</f>
-        <v/>
-      </c>
-      <c r="P12" s="59">
-        <f>ROUNDUP(P11/30,0)</f>
-        <v/>
-      </c>
-      <c r="Q12" s="59">
-        <f>ROUNDUP(Q11/30,0)</f>
-        <v/>
-      </c>
-      <c r="R12" s="59">
-        <f>ROUNDUP(R11/30,0)</f>
-        <v/>
-      </c>
-      <c r="S12" s="59">
-        <f>ROUNDUP(S11/30,0)</f>
-        <v/>
-      </c>
-      <c r="T12" s="59">
-        <f>ROUNDUP(T11/30,0)</f>
-        <v/>
-      </c>
-      <c r="U12" s="59">
-        <f>ROUNDUP(U11/30,0)</f>
-        <v/>
-      </c>
-      <c r="V12" s="59">
-        <f>ROUNDUP(V11/30,0)</f>
-        <v/>
-      </c>
-      <c r="W12" s="59">
-        <f>ROUNDUP(W11/30,0)</f>
-        <v/>
-      </c>
-      <c r="X12" s="59">
-        <f>ROUNDUP(X11/30,0)</f>
-        <v/>
-      </c>
-      <c r="Y12" s="59">
-        <f>ROUNDUP(Y11/30,0)</f>
-        <v/>
-      </c>
-      <c r="Z12" s="59">
-        <f>ROUNDUP(Z11/30,0)</f>
-        <v/>
-      </c>
-      <c r="AA12" s="59">
-        <f>ROUNDUP(AA11/30,0)</f>
-        <v/>
-      </c>
-      <c r="AB12" s="59">
-        <f>ROUNDUP(AB11/30,0)</f>
-        <v/>
-      </c>
-      <c r="AC12" s="59">
-        <f>ROUNDUP(AC11/30,0)</f>
-        <v/>
-      </c>
-      <c r="AD12" s="59">
-        <f>ROUNDUP(AD11/30,0)</f>
-        <v/>
-      </c>
-      <c r="AE12" s="59">
-        <f>ROUNDUP(AE11/30,0)</f>
-        <v/>
-      </c>
-      <c r="AF12" s="59">
-        <f>ROUNDUP(AF11/30,0)</f>
-        <v/>
-      </c>
-      <c r="AG12" s="59">
-        <f>ROUNDUP(AG11/30,0)</f>
-        <v/>
-      </c>
-      <c r="AH12" s="59">
-        <f>ROUNDUP(AH11/30,0)</f>
-        <v/>
-      </c>
-      <c r="AI12" s="59">
-        <f>ROUNDUP(AI11/30,0)</f>
-        <v/>
-      </c>
-      <c r="AJ12" s="59">
-        <f>ROUNDUP(AJ11/30,0)</f>
-        <v/>
-      </c>
-      <c r="AK12" s="59">
-        <f>ROUNDUP(AK11/30,0)</f>
-        <v/>
-      </c>
-      <c r="AL12" s="59">
-        <f>ROUNDUP(AL11/30,0)</f>
-        <v/>
-      </c>
-      <c r="AM12" s="59">
-        <f>ROUNDUP(AM11/30,0)</f>
-        <v/>
-      </c>
-      <c r="AN12" s="59">
-        <f>ROUNDUP(AN11/30,0)</f>
-        <v/>
-      </c>
-      <c r="AP12" s="57" t="inlineStr">
-        <is>
-          <t>loads/day at 30 m³ a tanker. If this number is above one or two, a connection or a package plant stops being optional.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Electrical connected load</t>
-        </is>
-      </c>
-      <c r="C14" s="60">
-        <f>ROUND(BedDemand!C10*Assumptions!$C$54+IF(BedDemand!C10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="D14" s="60">
-        <f>ROUND(BedDemand!D10*Assumptions!$C$54+IF(BedDemand!D10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="E14" s="60">
-        <f>ROUND(BedDemand!E10*Assumptions!$C$54+IF(BedDemand!E10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="F14" s="60">
-        <f>ROUND(BedDemand!F10*Assumptions!$C$54+IF(BedDemand!F10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="G14" s="60">
-        <f>ROUND(BedDemand!G10*Assumptions!$C$54+IF(BedDemand!G10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="H14" s="60">
-        <f>ROUND(BedDemand!H10*Assumptions!$C$54+IF(BedDemand!H10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="I14" s="60">
-        <f>ROUND(BedDemand!I10*Assumptions!$C$54+IF(BedDemand!I10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="J14" s="60">
-        <f>ROUND(BedDemand!J10*Assumptions!$C$54+IF(BedDemand!J10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="K14" s="60">
-        <f>ROUND(BedDemand!K10*Assumptions!$C$54+IF(BedDemand!K10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="L14" s="60">
-        <f>ROUND(BedDemand!L10*Assumptions!$C$54+IF(BedDemand!L10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="M14" s="60">
-        <f>ROUND(BedDemand!M10*Assumptions!$C$54+IF(BedDemand!M10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="N14" s="60">
-        <f>ROUND(BedDemand!N10*Assumptions!$C$54+IF(BedDemand!N10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="O14" s="60">
-        <f>ROUND(BedDemand!O10*Assumptions!$C$54+IF(BedDemand!O10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="P14" s="60">
-        <f>ROUND(BedDemand!P10*Assumptions!$C$54+IF(BedDemand!P10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="Q14" s="60">
-        <f>ROUND(BedDemand!Q10*Assumptions!$C$54+IF(BedDemand!Q10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="R14" s="60">
-        <f>ROUND(BedDemand!R10*Assumptions!$C$54+IF(BedDemand!R10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="S14" s="60">
-        <f>ROUND(BedDemand!S10*Assumptions!$C$54+IF(BedDemand!S10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="T14" s="60">
-        <f>ROUND(BedDemand!T10*Assumptions!$C$54+IF(BedDemand!T10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="U14" s="60">
-        <f>ROUND(BedDemand!U10*Assumptions!$C$54+IF(BedDemand!U10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="V14" s="60">
-        <f>ROUND(BedDemand!V10*Assumptions!$C$54+IF(BedDemand!V10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="W14" s="60">
-        <f>ROUND(BedDemand!W10*Assumptions!$C$54+IF(BedDemand!W10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="X14" s="60">
-        <f>ROUND(BedDemand!X10*Assumptions!$C$54+IF(BedDemand!X10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="Y14" s="60">
-        <f>ROUND(BedDemand!Y10*Assumptions!$C$54+IF(BedDemand!Y10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="Z14" s="60">
-        <f>ROUND(BedDemand!Z10*Assumptions!$C$54+IF(BedDemand!Z10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="AA14" s="60">
-        <f>ROUND(BedDemand!AA10*Assumptions!$C$54+IF(BedDemand!AA10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="AB14" s="60">
-        <f>ROUND(BedDemand!AB10*Assumptions!$C$54+IF(BedDemand!AB10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="AC14" s="60">
-        <f>ROUND(BedDemand!AC10*Assumptions!$C$54+IF(BedDemand!AC10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="AD14" s="60">
-        <f>ROUND(BedDemand!AD10*Assumptions!$C$54+IF(BedDemand!AD10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="AE14" s="60">
-        <f>ROUND(BedDemand!AE10*Assumptions!$C$54+IF(BedDemand!AE10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="AF14" s="60">
-        <f>ROUND(BedDemand!AF10*Assumptions!$C$54+IF(BedDemand!AF10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="AG14" s="60">
-        <f>ROUND(BedDemand!AG10*Assumptions!$C$54+IF(BedDemand!AG10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="AH14" s="60">
-        <f>ROUND(BedDemand!AH10*Assumptions!$C$54+IF(BedDemand!AH10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="AI14" s="60">
-        <f>ROUND(BedDemand!AI10*Assumptions!$C$54+IF(BedDemand!AI10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="AJ14" s="60">
-        <f>ROUND(BedDemand!AJ10*Assumptions!$C$54+IF(BedDemand!AJ10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="AK14" s="60">
-        <f>ROUND(BedDemand!AK10*Assumptions!$C$54+IF(BedDemand!AK10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="AL14" s="60">
-        <f>ROUND(BedDemand!AL10*Assumptions!$C$54+IF(BedDemand!AL10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="AM14" s="60">
-        <f>ROUND(BedDemand!AM10*Assumptions!$C$54+IF(BedDemand!AM10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="AN14" s="60">
-        <f>ROUND(BedDemand!AN10*Assumptions!$C$54+IF(BedDemand!AN10&gt;0,Assumptions!$C$56,0),0)</f>
-        <v/>
-      </c>
-      <c r="AP14" s="57" t="inlineStr">
-        <is>
-          <t>kW. Accommodation plus catering. Excludes electric space heating, which is on the line below.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Heating load</t>
-        </is>
-      </c>
-      <c r="C15" s="60">
-        <f>ROUND(BedDemand!C10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="D15" s="60">
-        <f>ROUND(BedDemand!D10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="E15" s="60">
-        <f>ROUND(BedDemand!E10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="F15" s="60">
-        <f>ROUND(BedDemand!F10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="G15" s="60">
-        <f>ROUND(BedDemand!G10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="H15" s="60">
-        <f>ROUND(BedDemand!H10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="I15" s="60">
-        <f>ROUND(BedDemand!I10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="J15" s="60">
-        <f>ROUND(BedDemand!J10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="K15" s="60">
-        <f>ROUND(BedDemand!K10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="L15" s="60">
-        <f>ROUND(BedDemand!L10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="M15" s="60">
-        <f>ROUND(BedDemand!M10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="N15" s="60">
-        <f>ROUND(BedDemand!N10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="O15" s="60">
-        <f>ROUND(BedDemand!O10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="P15" s="60">
-        <f>ROUND(BedDemand!P10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="Q15" s="60">
-        <f>ROUND(BedDemand!Q10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="R15" s="60">
-        <f>ROUND(BedDemand!R10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="S15" s="60">
-        <f>ROUND(BedDemand!S10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="T15" s="60">
-        <f>ROUND(BedDemand!T10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="U15" s="60">
-        <f>ROUND(BedDemand!U10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="V15" s="60">
-        <f>ROUND(BedDemand!V10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="W15" s="60">
-        <f>ROUND(BedDemand!W10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="X15" s="60">
-        <f>ROUND(BedDemand!X10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="Y15" s="60">
-        <f>ROUND(BedDemand!Y10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="Z15" s="60">
-        <f>ROUND(BedDemand!Z10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="AA15" s="60">
-        <f>ROUND(BedDemand!AA10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="AB15" s="60">
-        <f>ROUND(BedDemand!AB10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="AC15" s="60">
-        <f>ROUND(BedDemand!AC10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="AD15" s="60">
-        <f>ROUND(BedDemand!AD10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="AE15" s="60">
-        <f>ROUND(BedDemand!AE10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="AF15" s="60">
-        <f>ROUND(BedDemand!AF10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="AG15" s="60">
-        <f>ROUND(BedDemand!AG10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="AH15" s="60">
-        <f>ROUND(BedDemand!AH10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="AI15" s="60">
-        <f>ROUND(BedDemand!AI10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="AJ15" s="60">
-        <f>ROUND(BedDemand!AJ10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="AK15" s="60">
-        <f>ROUND(BedDemand!AK10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="AL15" s="60">
-        <f>ROUND(BedDemand!AL10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="AM15" s="60">
-        <f>ROUND(BedDemand!AM10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="AN15" s="60">
-        <f>ROUND(BedDemand!AN10*Assumptions!$C$57,0)</f>
-        <v/>
-      </c>
-      <c r="AP15" s="57" t="inlineStr">
-        <is>
-          <t>kW at design outside temperature. Verify against the module supplier's U-values and the fuel you actually use.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Diversified demand</t>
-        </is>
-      </c>
-      <c r="C16" s="60">
-        <f>ROUND(C14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="D16" s="60">
-        <f>ROUND(D14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="E16" s="60">
-        <f>ROUND(E14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="F16" s="60">
-        <f>ROUND(F14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="G16" s="60">
-        <f>ROUND(G14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="H16" s="60">
-        <f>ROUND(H14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="I16" s="60">
-        <f>ROUND(I14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="J16" s="60">
-        <f>ROUND(J14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="K16" s="60">
-        <f>ROUND(K14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="L16" s="60">
-        <f>ROUND(L14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="M16" s="60">
-        <f>ROUND(M14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="N16" s="60">
-        <f>ROUND(N14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="O16" s="60">
-        <f>ROUND(O14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="P16" s="60">
-        <f>ROUND(P14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="Q16" s="60">
-        <f>ROUND(Q14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="R16" s="60">
-        <f>ROUND(R14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="S16" s="60">
-        <f>ROUND(S14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="T16" s="60">
-        <f>ROUND(T14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="U16" s="60">
-        <f>ROUND(U14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="V16" s="60">
-        <f>ROUND(V14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="W16" s="60">
-        <f>ROUND(W14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="X16" s="60">
-        <f>ROUND(X14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="Y16" s="60">
-        <f>ROUND(Y14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="Z16" s="60">
-        <f>ROUND(Z14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="AA16" s="60">
-        <f>ROUND(AA14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="AB16" s="60">
-        <f>ROUND(AB14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="AC16" s="60">
-        <f>ROUND(AC14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="AD16" s="60">
-        <f>ROUND(AD14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="AE16" s="60">
-        <f>ROUND(AE14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="AF16" s="60">
-        <f>ROUND(AF14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="AG16" s="60">
-        <f>ROUND(AG14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="AH16" s="60">
-        <f>ROUND(AH14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="AI16" s="60">
-        <f>ROUND(AI14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="AJ16" s="60">
-        <f>ROUND(AJ14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="AK16" s="60">
-        <f>ROUND(AK14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="AL16" s="60">
-        <f>ROUND(AL14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="AM16" s="60">
-        <f>ROUND(AM14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="AN16" s="60">
-        <f>ROUND(AN14*Assumptions!$C$55,0)</f>
-        <v/>
-      </c>
-      <c r="AP16" s="57" t="inlineStr">
-        <is>
-          <t>kW. Not every load runs at once. The diversity factor is on Assumptions and needs an engineer's eye.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Diversified demand</t>
-        </is>
-      </c>
-      <c r="C17" s="60">
-        <f>ROUND(C16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="D17" s="60">
-        <f>ROUND(D16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="E17" s="60">
-        <f>ROUND(E16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="F17" s="60">
-        <f>ROUND(F16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="G17" s="60">
-        <f>ROUND(G16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="H17" s="60">
-        <f>ROUND(H16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="I17" s="60">
-        <f>ROUND(I16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="J17" s="60">
-        <f>ROUND(J16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="K17" s="60">
-        <f>ROUND(K16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="L17" s="60">
-        <f>ROUND(L16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="M17" s="60">
-        <f>ROUND(M16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="N17" s="60">
-        <f>ROUND(N16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="O17" s="60">
-        <f>ROUND(O16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="P17" s="60">
-        <f>ROUND(P16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="Q17" s="60">
-        <f>ROUND(Q16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="R17" s="60">
-        <f>ROUND(R16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="S17" s="60">
-        <f>ROUND(S16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="T17" s="60">
-        <f>ROUND(T16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="U17" s="60">
-        <f>ROUND(U16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="V17" s="60">
-        <f>ROUND(V16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="W17" s="60">
-        <f>ROUND(W16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="X17" s="60">
-        <f>ROUND(X16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="Y17" s="60">
-        <f>ROUND(Y16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="Z17" s="60">
-        <f>ROUND(Z16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="AA17" s="60">
-        <f>ROUND(AA16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="AB17" s="60">
-        <f>ROUND(AB16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="AC17" s="60">
-        <f>ROUND(AC16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="AD17" s="60">
-        <f>ROUND(AD16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="AE17" s="60">
-        <f>ROUND(AE16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="AF17" s="60">
-        <f>ROUND(AF16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="AG17" s="60">
-        <f>ROUND(AG16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="AH17" s="60">
-        <f>ROUND(AH16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="AI17" s="60">
-        <f>ROUND(AI16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="AJ17" s="60">
-        <f>ROUND(AJ16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="AK17" s="60">
-        <f>ROUND(AK16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="AL17" s="60">
-        <f>ROUND(AL16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="AM17" s="60">
-        <f>ROUND(AM16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="AN17" s="60">
-        <f>ROUND(AN16/Assumptions!$C$58,0)</f>
-        <v/>
-      </c>
-      <c r="AP17" s="57" t="inlineStr">
-        <is>
-          <t>kVA — the unit a DNO connection or a generator is actually sized in. Getting kW and kVA confused undersizes a village by a fifth.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Waste arisings</t>
-        </is>
-      </c>
-      <c r="C19" s="59">
-        <f>ROUND(BedDemand!C10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="D19" s="59">
-        <f>ROUND(BedDemand!D10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="E19" s="59">
-        <f>ROUND(BedDemand!E10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="F19" s="59">
-        <f>ROUND(BedDemand!F10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="G19" s="59">
-        <f>ROUND(BedDemand!G10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="H19" s="59">
-        <f>ROUND(BedDemand!H10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="I19" s="59">
-        <f>ROUND(BedDemand!I10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="J19" s="59">
-        <f>ROUND(BedDemand!J10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="K19" s="59">
-        <f>ROUND(BedDemand!K10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="L19" s="59">
-        <f>ROUND(BedDemand!L10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="M19" s="59">
-        <f>ROUND(BedDemand!M10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="N19" s="59">
-        <f>ROUND(BedDemand!N10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="O19" s="59">
-        <f>ROUND(BedDemand!O10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="P19" s="59">
-        <f>ROUND(BedDemand!P10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="Q19" s="59">
-        <f>ROUND(BedDemand!Q10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="R19" s="59">
-        <f>ROUND(BedDemand!R10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="S19" s="59">
-        <f>ROUND(BedDemand!S10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="T19" s="59">
-        <f>ROUND(BedDemand!T10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="U19" s="59">
-        <f>ROUND(BedDemand!U10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="V19" s="59">
-        <f>ROUND(BedDemand!V10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="W19" s="59">
-        <f>ROUND(BedDemand!W10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="X19" s="59">
-        <f>ROUND(BedDemand!X10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="Y19" s="59">
-        <f>ROUND(BedDemand!Y10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="Z19" s="59">
-        <f>ROUND(BedDemand!Z10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="AA19" s="59">
-        <f>ROUND(BedDemand!AA10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="AB19" s="59">
-        <f>ROUND(BedDemand!AB10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="AC19" s="59">
-        <f>ROUND(BedDemand!AC10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="AD19" s="59">
-        <f>ROUND(BedDemand!AD10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="AE19" s="59">
-        <f>ROUND(BedDemand!AE10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="AF19" s="59">
-        <f>ROUND(BedDemand!AF10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="AG19" s="59">
-        <f>ROUND(BedDemand!AG10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="AH19" s="59">
-        <f>ROUND(BedDemand!AH10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="AI19" s="59">
-        <f>ROUND(BedDemand!AI10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="AJ19" s="59">
-        <f>ROUND(BedDemand!AJ10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="AK19" s="59">
-        <f>ROUND(BedDemand!AK10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="AL19" s="59">
-        <f>ROUND(BedDemand!AL10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="AM19" s="59">
-        <f>ROUND(BedDemand!AM10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="AN19" s="59">
-        <f>ROUND(BedDemand!AN10*Assumptions!$C$59/1000*30.4,1)</f>
-        <v/>
-      </c>
-      <c r="AP19" s="57" t="inlineStr">
-        <is>
-          <t>tonnes/month. Residential plus catering.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  recycled or diverted</t>
-        </is>
-      </c>
-      <c r="C20" s="59">
-        <f>ROUND(C19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="D20" s="59">
-        <f>ROUND(D19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="E20" s="59">
-        <f>ROUND(E19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="F20" s="59">
-        <f>ROUND(F19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="G20" s="59">
-        <f>ROUND(G19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="H20" s="59">
-        <f>ROUND(H19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="I20" s="59">
-        <f>ROUND(I19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="J20" s="59">
-        <f>ROUND(J19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="K20" s="59">
-        <f>ROUND(K19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="L20" s="59">
-        <f>ROUND(L19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="M20" s="59">
-        <f>ROUND(M19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="N20" s="59">
-        <f>ROUND(N19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="O20" s="59">
-        <f>ROUND(O19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="P20" s="59">
-        <f>ROUND(P19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="Q20" s="59">
-        <f>ROUND(Q19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="R20" s="59">
-        <f>ROUND(R19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="S20" s="59">
-        <f>ROUND(S19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="T20" s="59">
-        <f>ROUND(T19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="U20" s="59">
-        <f>ROUND(U19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="V20" s="59">
-        <f>ROUND(V19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="W20" s="59">
-        <f>ROUND(W19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="X20" s="59">
-        <f>ROUND(X19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="Y20" s="59">
-        <f>ROUND(Y19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="Z20" s="59">
-        <f>ROUND(Z19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="AA20" s="59">
-        <f>ROUND(AA19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="AB20" s="59">
-        <f>ROUND(AB19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="AC20" s="59">
-        <f>ROUND(AC19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="AD20" s="59">
-        <f>ROUND(AD19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="AE20" s="59">
-        <f>ROUND(AE19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="AF20" s="59">
-        <f>ROUND(AF19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="AG20" s="59">
-        <f>ROUND(AG19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="AH20" s="59">
-        <f>ROUND(AH19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="AI20" s="59">
-        <f>ROUND(AI19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="AJ20" s="59">
-        <f>ROUND(AJ19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="AK20" s="59">
-        <f>ROUND(AK19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="AL20" s="59">
-        <f>ROUND(AL19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="AM20" s="59">
-        <f>ROUND(AM19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="AN20" s="59">
-        <f>ROUND(AN19*Assumptions!$C$60,1)</f>
-        <v/>
-      </c>
-      <c r="AP20" s="57" t="inlineStr">
-        <is>
-          <t>tonnes/month against the target on Assumptions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>General waste collections</t>
-        </is>
-      </c>
-      <c r="C21" s="37">
-        <f>ROUNDUP(C19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="D21" s="37">
-        <f>ROUNDUP(D19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="E21" s="37">
-        <f>ROUNDUP(E19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="F21" s="37">
-        <f>ROUNDUP(F19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="G21" s="37">
-        <f>ROUNDUP(G19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="H21" s="37">
-        <f>ROUNDUP(H19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="I21" s="37">
-        <f>ROUNDUP(I19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="J21" s="37">
-        <f>ROUNDUP(J19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="K21" s="37">
-        <f>ROUNDUP(K19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="L21" s="37">
-        <f>ROUNDUP(L19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="M21" s="37">
-        <f>ROUNDUP(M19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="N21" s="37">
-        <f>ROUNDUP(N19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="O21" s="37">
-        <f>ROUNDUP(O19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="P21" s="37">
-        <f>ROUNDUP(P19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="Q21" s="37">
-        <f>ROUNDUP(Q19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="R21" s="37">
-        <f>ROUNDUP(R19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="S21" s="37">
-        <f>ROUNDUP(S19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="T21" s="37">
-        <f>ROUNDUP(T19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="U21" s="37">
-        <f>ROUNDUP(U19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="V21" s="37">
-        <f>ROUNDUP(V19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="W21" s="37">
-        <f>ROUNDUP(W19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="X21" s="37">
-        <f>ROUNDUP(X19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="Y21" s="37">
-        <f>ROUNDUP(Y19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="Z21" s="37">
-        <f>ROUNDUP(Z19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="AA21" s="37">
-        <f>ROUNDUP(AA19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="AB21" s="37">
-        <f>ROUNDUP(AB19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="AC21" s="37">
-        <f>ROUNDUP(AC19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="AD21" s="37">
-        <f>ROUNDUP(AD19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="AE21" s="37">
-        <f>ROUNDUP(AE19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="AF21" s="37">
-        <f>ROUNDUP(AF19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="AG21" s="37">
-        <f>ROUNDUP(AG19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="AH21" s="37">
-        <f>ROUNDUP(AH19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="AI21" s="37">
-        <f>ROUNDUP(AI19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="AJ21" s="37">
-        <f>ROUNDUP(AJ19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="AK21" s="37">
-        <f>ROUNDUP(AK19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="AL21" s="37">
-        <f>ROUNDUP(AL19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="AM21" s="37">
-        <f>ROUNDUP(AM19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="AN21" s="37">
-        <f>ROUNDUP(AN19*1000/1100/12,0)</f>
-        <v/>
-      </c>
-      <c r="AP21" s="57" t="inlineStr">
-        <is>
-          <t>collections/month at 1100 l bins, twelve per collection. Indicative — set against the contractor's actual round.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="39" t="inlineStr">
-        <is>
-          <t>PEAK — WHAT YOU DESIGN AND PROCURE AGAINST</t>
-        </is>
-      </c>
-      <c r="C23" s="40" t="n"/>
-      <c r="D23" s="40" t="n"/>
-      <c r="E23" s="40" t="n"/>
-      <c r="F23" s="40" t="n"/>
-      <c r="G23" s="40" t="n"/>
-      <c r="H23" s="40" t="n"/>
-      <c r="I23" s="40" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Peak water demand</t>
-        </is>
-      </c>
-      <c r="C24" s="61">
-        <f>MAX(C9:AN9)</f>
-        <v/>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>m³/day — the figure that goes on the water undertaker's enquiry.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Peak foul return</t>
-        </is>
-      </c>
-      <c r="C25" s="61">
-        <f>MAX(C11:AN11)</f>
-        <v/>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>m³/day — treatment plant or tanker capacity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Peak connected load</t>
-        </is>
-      </c>
-      <c r="C26" s="62">
-        <f>MAX(C14:AN14)</f>
-        <v/>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>kW.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Peak diversified demand</t>
-        </is>
-      </c>
-      <c r="C27" s="62">
-        <f>MAX(C17:AN17)</f>
-        <v/>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>kVA — the figure that goes on the DNO application or the generator enquiry.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Peak waste arisings</t>
-        </is>
-      </c>
-      <c r="C28" s="61">
-        <f>MAX(C19:AN19)</f>
-        <v/>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>tonnes/month.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="63" t="inlineStr">
-        <is>
-          <t>Every figure on this sheet is a first-pass planning figure requiring validation by a competent person before it is procured against.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>